--- a/egs_aide/看盘神器/v1/看盘模板.xlsx
+++ b/egs_aide/看盘神器/v1/看盘模板.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jerry/workspace/ai_quant_trade/egs_aide/看盘神器/v1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF0CFCF1-9910-444E-9C3A-04CCE6FA89CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0120823-EBBA-DA48-B349-62F909A8139B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="40960" windowHeight="25000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1455" uniqueCount="1319">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1454" uniqueCount="1318">
   <si>
     <t>代码</t>
   </si>
@@ -4661,208 +4661,311 @@
     <t>云维股份</t>
   </si>
   <si>
+    <t>中国石油</t>
+  </si>
+  <si>
+    <t>美政府正酝酿征收新关税</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>【美政府正酝酿征收新关税】财联社2月26日电，美国最高法院近日裁定美国政府的大规模关税政策非法，多家美国媒体日前披露说，美国政府正准备援引其他法律条款对多个行业产品加征新的关税。在美国最高法院作出相关裁决之后，包括美国联邦快递公司、开市客、锐步等大型美国企业在内的上千家企业在美国国际贸易法院提起诉讼，要求政府返还已缴纳的关税。纽约州、加利福尼亚州和伊利诺伊州等州政府也向联邦政府提出退还关税的要求。 (CCTV国际时讯)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>财联社2月26日电，美联储官员巴尔金称，利率政策无法应对人工智能带来的冲击。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>财联社2月26日电，美国电动汽车公司Rivian与CrunchLabs宣布达成独家合作伙伴关系。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>财联社2月25日电，谷歌称，聊天功能现已作为数据源在Gemini应用中可用。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>摩根士丹利称人工智能恐慌为选股者创造机遇</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>【摩根士丹利称人工智能恐慌为选股者创造机遇】财联社2月25日电，摩根士丹利策略师表示，对人工智能带来颠覆的担忧引发的各板块过度抛售，为选股者创造了机会。Andrew Pauker等策略师表示，投资者应寻找该团队所说的“人工智能既有优势者”、高增长股以及高质量个股，以把握价格回落以及技术普及带来的动能。对那些定价权强、积极采用AI的公司而言，其投资逻辑仍在增强。Pauker写道：“短期内人工智能的普及有助于抵消对受影响领域以及整体市场受到更长期颠覆的担忧。”软件股一直是受投资者恐慌情绪冲击最严重的板块之一，策略师指出，市场似乎已假设行业龙头无法从人工智能创新中获益。相反，他们认为人工智能将扩大企业软件的可服务市场，并称微软、财捷集团和Atlassian Corp.等个股存在“有吸引力的入场点”。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>财联社2月25日电，纳斯达克中国金龙指数跌幅扩大，现跌1.0%，最新报7504.6点。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
     <t>庐山风景区：3月全体海内外游客免门票</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>【庐山风景区：3月全体海内外游客免门票】财联社2月25日电，“中国庐山发布”微信公众号发布《关于庐山风景区2026年三月份对全体海内外游客免收门票的通告》。公告显示，为巩固和扩大文旅消费，回馈广大游客对庐山的厚爱，2026年3月份庐山风景区对全体海内外游客免收门票。免票范围包括庐山风景区（5A级）、三叠泉、白鹿洞书院、观音桥、秀峰、碧龙潭、桃花源、石门涧景区入园门票（不含观光车、索道等景区二次消费项目）。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>美国上周EIA原油库存增加1598.9万桶</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>【美国上周EIA原油库存增加1598.9万桶】财联社2月25日电，美国上周EIA原油库存增加1598.9万桶，预期增加192.5万桶，前值减少901.4万桶。美国上周EIA库欣地区原油库存变动增加88.1万桶，前值减少109.5万桶。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>美方公布新一轮涉伊朗制裁名单</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>【美方公布新一轮涉伊朗制裁名单】财联社2月25日电，美国财政部海外资产控制办公室（OFAC）更新“特别指定国民清单”，对与伊朗相关的多名个人、实体及多艘船只实施相关制裁。本轮制裁对象包括4名伊朗籍个人，均与伊朗航空工业企业有关；多家位于伊朗、土耳其、阿联酋、巴拿马、马绍尔群岛、利比里亚等地的航运及贸易公司被列入名单，涉及伊朗石油与液化气运输网络；至少13艘油轮和液化气运输船被列入制裁范围，相关船只悬挂巴拿马、帕劳、巴巴多斯、瓦努阿图、科摩罗及伊朗等国旗。美国财政部表示，上述个人与实体将面临资产冻结及与美国金融体系交易限制。 (央视新闻)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>挪威首相称将向乌克兰提供约850亿挪威克朗援助</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>【挪威首相称将向乌克兰提供约850亿挪威克朗援助】财联社2月25日电，挪威首相斯特勒在基辅与乌克兰总统泽连斯基共同举行的新闻发布会上宣布，挪威将在2026年向乌克兰提供约850亿挪威克朗（约合607亿元人民币）的援助。他表示，这笔金额约占乌克兰今年所获援助总额的20%。斯特勒表示：“今天，我和总统就挪威和乌克兰之间的战略伙伴关系达成了一致。”目前合作细节尚不清楚，但斯特勒表示，双方将共同开发能够互惠互利的各个领域。 (央视新闻)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>玉渊谭天：商务部此次对日本管制措施有三个特点值得注意</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>【玉渊谭天：商务部此次对日本管制措施有三个特点值得注意】财联社2月25日电，“玉渊谭天”发文称，2026年2月24日，商务部依法将40家日本实体分别列入出口管制管控名单和关注名单，并同步出台针对性出口管制措施。这是今年1月商务部发布关于加强两用物项对日本出口管制的公告后，又一次出手。商务部此次措施，有三点值得注意：其一，首次启用关注名单制度，开启我国出口管制精准治理新路径。其二，对管控名单的实体采取严格禁止措施，彰显制止日本“再军事化”和拥核图谋的坚定立场。其三，此次措施是1号公告的升级版。当前，全球化遭遇逆流，地区安全风险加剧，但中国的工具箱也在快速充实，应对侵犯我合法利益的行为，中方将时刻准备着予以反击。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>存储概念涨势扩大 西部数据涨超7%</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>【存储概念涨势扩大 西部数据涨超7%】财联社2月25日电，存储概念涨势扩大，西部数据涨超7%，希捷科技涨超4%，美光科技涨超3%，闪迪涨超1%。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>瑞银财富管理美洲首席投资官建议：AI热潮中弃科技奔实体</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>【瑞银财富管理美洲首席投资官建议：AI热潮中弃科技奔实体】财联社2月25日电，瑞银财富管理美洲区首席投资官兼全球股票主管Ulrike Hoffmann-Burchardi表示，人工智能对以软件为基础的企业构成的威胁，应促使投资者将关注重点从科技公司转向那些深耕实体领域的企业，例如矿业公司、电力生产商和工业企业。她周二在迈阿密海滩出席一场金融行业会议间隙表示，其团队正着手将投资组合从聚焦“数字经济”转向“实体经济”。这意味着买入设备制造商、电力发电企业和资源类矿业公司等股票，即那些为现代经济运转构建实体基础设施的企业。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>国内商品期市夜盘收盘多数下跌 化工品跌幅居前</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>【国内商品期市夜盘收盘多数下跌 化工品跌幅居前】财联社2月25日电，国内商品期市夜盘收盘多数下跌，化工品跌幅居前，丁二烯橡胶跌2.58%；非金属建材全部下跌，PVC跌1.07%；油脂油料全部下跌，棕榈油跌0.77%；黑色系多数下跌，焦煤跌0.40%；能源品涨幅居前，LPG涨1.41%；农副产品多数上涨，白糖涨1.01%。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>锦欣康养产业集团有限公司递表港交所</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>【锦欣康养产业集团有限公司递表港交所】财联社2月25日电，利弗莫尔证券显示，锦欣康养产业集团有限公司向港交所提交上市申请书，联席保荐人为中金公司、广发证券。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>英国或暂停向毛里求斯移交查戈斯群岛主权进程</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>【英国或暂停向毛里求斯移交查戈斯群岛主权进程】财联社2月25日电，英国外交部官员称，英国或“暂停”将查戈斯群岛主权移交给毛里求斯的进程，同时与美国“直接就此进行商讨”。查戈斯群岛位于毛里求斯东北方向约750公里的印度洋西南海域，1965年被割让给英国殖民当局。英国次年把迪戈加西亚岛租给美国建空军基地。2025年5月22日，英国和毛里求斯签署协议，查戈斯群岛主权被正式移交给毛里求斯。根据协议，迪戈加西亚军事基地将由毛里求斯租借给英国和美国。 (央视新闻)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>财联社2月25日电，纳斯达克100指数涨幅扩大至1%。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>福建：健全完善民企涉外服务机制 降低跨境商务成本</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>【福建：健全完善民企涉外服务机制 降低跨境商务成本】财联社2月25日电，福建省全面实施新时代民营经济强省战略领导小组第五次会议25日召开。会议强调，要进一步提升外事港澳资源服务企业“走出去”的精准度和实效性，支持民企深度融入高质量共建“一带一路”，更好融入全球市场网络；健全完善民企涉外服务机制，降低跨境商务成本，促进人员便利往来；推动外事资源与企业需求高效匹配，搭建高层次产学研对接平台，推动更多科技成果在我省民营企业转化；完善海外权益保护与风险防控体系，助力提升企业应对风险能力。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>财联社2月25日电，WTI原油价格转跌，跌破每桶66美元，此前曾上涨约1%。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>华策影视辟谣“解散电影部门”：不实传闻，2026年电影业务将全面升级</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>【华策影视辟谣“解散电影部门”：不实传闻，2026年电影业务将全面升级】财联社2月25日电，针对近期网络上出现的“华策影视解散电影部门”消息，华策影视相关负责人今日晚间发表声明称，相关信息无事实依据。公司表示，正在全面推进“内容+科技”战略升级，将人工智能技术作为驱动内容创作创新的核心动力，对包括电影业务在内的全内容板块进行转型升级。2026年，电影业务将全面升级，不再盲目追求规模，而是坚守“收支平衡”的底线，优先修复现金流。（财联社记者 陈抗）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>伯特利：拟收购豫北转向控股权</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>【伯特利：拟收购豫北转向控股权】财联社2月25日电，伯特利(603596.SH)公告称，公司拟与豫北转向之股东峻鸿实业、宁波奉元、合肥华芯、合肥产投等相关方共同签署《股份转让协议》，合计收购各转让方所持豫北转向50.9727%的股份。本次收购完成后，伯特利将成为豫北转向的控股股东。豫北转向主要从事汽车转向系统及其关键零部件的研发、生产和销售。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>美股锂矿概念股走强</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>【美股锂矿概念股走强】财联社2月25日电，美股锂矿概念股走强，Sigma Lithium大涨27%，美国雅保涨9.91%，Lithium Argentina AG涨超7%。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>财联社2月25日电，利弗莫尔中概股龙头指数盘初跌0.1%。成分股中，百济神州跌超3%，腾讯音乐、小鹏汽车、网易跌超2%。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>纳指高开0.6%</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>【纳指高开0.6%】财联社2月25日电，美股三大指数集体高开，纳指涨0.62%，道指涨0.35%，标普500指数涨0.44%。即将在收盘后公布财报的英伟达高开0.8%。加密货币概念股普涨，Circle涨超20%。存储概念股走高，希捷科技、西部数据涨超3%。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>农业农村部部长韩俊：将统筹建立常态化防止返贫致贫机制</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>【农业农村部部长韩俊：将统筹建立常态化防止返贫致贫机制】财联社2月25日电，过渡期后，将如何继续发力，做到常态化防止返贫致贫，推进乡村全面振兴？农业农村部党组书记、部长韩俊在接受采访时表示，按照党中央部署，下一步将统筹建立常态化防止返贫致贫机制，把常态化帮扶纳入乡村振兴战略统筹实施，以有力有效的开发式帮扶增强内生发展动力，以健全完备的社会保障体系兜牢民生底线，长久守牢不发生规模性返贫致贫的底线。重点从以下几方面发力。一是实施常态化监测帮扶。二是提升开发式帮扶效能。三是分层分类帮扶欠发达地区。四是稳定并完善常态化帮扶政策体系。 (新华社)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>美军一运输机在菲律宾演习时发生着陆事故</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>【美军一运输机在菲律宾演习时发生着陆事故】财联社2月25日电，菲律宾军方2月25日表示，一架美国空军的C-146运输机24日在菲律宾邦阿西楠省拉瓦克镇参与联合公路着陆演习时发生着陆事故，所有飞行员及机组人员均已确认安全无恙，无平民受伤。事故调查正在进行当中。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>【公告全知道】PCB+芯片+机器人+锂电池+光伏！公司产品在PCB、锂电等领域已规模化替代进口设备</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>①PCB+芯片+机器人+锂电池+光伏！这家公司产品在PCB、锂电等领域已规模化替代进口设备；②CPO+PCB+固态电池+PET铜箔！这家公司拟投资5亿元获取光模块企业部分股权；③商业航天+算力+卫星导航！公司参股企业计划2031年至2035年卫星大规模批量生产并组网发射且在轨对接建成大规模太空数据中心。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>伊朗外长启程赴日内瓦参加伊美新一轮间接谈判</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>【伊朗外长启程赴日内瓦参加伊美新一轮间接谈判】财联社2月25日电，据伊朗塔斯尼姆通讯社报道，伊朗外交部长阿拉格齐25日率领政治代表团离开首都德黑兰前往瑞士日内瓦，参加与美国的新一轮间接谈判。在阿曼斡旋下，伊朗与美国第三轮间接谈判将于26日在日内瓦举行。美国和伊朗第二轮间接谈判17日在日内瓦举行。美伊官员在谈判结束后均表示，尽管分歧仍存，但谈判较上一轮取得进展，双方同意继续接触。美国近期在中东地区大规模集结兵力。美国总统特朗普近日承认，他在考虑对伊朗进行“有限军事打击”。 (新华社)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>财政部副部长廖岷：G20各方应坚定维护多边主义和自由贸易 把握数字经济、绿色转型和人工智能等增长机遇</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>【财政部副部长廖岷：G20各方应坚定维护多边主义和自由贸易 把握数字经济、绿色转型和人工智能等增长机遇】财联社2月25日电，2026年二十国集团（G20）主席国美国25日以视频方式举行其接任主席国后的第二次G20财政和央行副手会议，G20成员国、嘉宾国财金副手及国际组织代表参会。会议重点围绕全球增长问题进行讨论。美国主席国介绍了全球失衡、国际债务、金融素养等今年G20财金渠道合作重点议题有关情况。财政部副部长廖岷表示，在全球经济不确定性上升背景下，提高生产率并实现强劲增长受到各方普遍关注。G20应将发展置于全球宏观政策框架的突出位置，通过加强宏观经济政策合作和有益经验交流为促进全球增长提供推动力。各方应坚定维护多边主义和自由贸易，支持普惠包容的经济全球化，反对贸易保护主义和单边主义，积极推进结构性改革，把握数字经济、绿色转型和人工智能等增长机遇，提升经济韧性、培育增长新动能。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>财联社2月25日电，美国银行表示，白银价格今年可能再次升至每盎司100美元以上。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>财联社2月25日电，IBM表示，已获得美国国防部一份为期最长五年、合同上限价值为1.12亿美元的合同。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>泽连斯基：乌美明日将讨论结束俄乌冲突步骤等问题</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>【泽连斯基：乌美明日将讨论结束俄乌冲突步骤等问题】财联社2月25日电，乌克兰总统泽连斯基25日在与挪威首相斯特勒举行的联合发布会上表示，即将在瑞士日内瓦与美国代表团进行的谈判中，乌方不仅会提出涉及结束俄乌冲突的问题，还会提出与美国进行经济合作等相关议题。他表示，目前乌谈判代表团负责人、乌国家安全与国防委员会秘书乌梅罗夫正在前往瑞士的途中，26日乌美代表团将举行双边会晤，共同起草一份经济文件。与此同时，正在制定一项包含20项内容的计划、安全保障措施以及一揽子重建方案，乌经济团队将参与。泽连斯基表示，在26日的会谈中，将会提出结束俄乌冲突的步骤顺序问题。他还表示，不确定26日能否在领土等问题上得到明确的结果，这些问题应该由领导人层级的会谈来讨论。 (央视新闻)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>财联社2月25日电，亚马逊推出Alexa的个性风格，提供多种定制化方式，让Alexa回应问题和请求时更具个性化。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>天辰生物医药（苏州）股份有限公司递表港交所</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>【天辰生物医药（苏州）股份有限公司递表港交所】财联社2月25日电，利弗莫尔证券显示，天辰生物医药（苏州）股份有限公司向港交所提交上市申请书，独家保荐人为国金证券（香港）。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>美贸易代表：美对部分国家加征的“全球进口关税”税率或达15%</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>【美贸易代表：美对部分国家加征的“全球进口关税”税率或达15%】财联社2月25日电，美国贸易代表贾米森·格里尔2月25日表示，美国对部分国家加征的“全球进口关税”税率将从新近实施的10%升至15%或更高，但他未透露任何具体的贸易伙伴或其他细节。20日，美国最高法院裁定，特朗普政府依据《国际紧急经济权力法》实施的相关大规模关税措施缺乏明确法律授权。当天，美最高法院大法官以6比3的结果维持下级法院裁决，认定特朗普援引《国际紧急经济权力法》实施关税政策超出了其法定权限。最高法院是在企业及美国12个州提起的诉讼中作出这一结论的。这些企业和州认为，特朗普以这一法律为依据，单方面征收进口税的做法前所未有。 (央视新闻)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>俄侦查委员会：乌军无人机袭击俄一化工厂致7人死亡</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>【俄侦查委员会：乌军无人机袭击俄一化工厂致7人死亡】财联社2月25日电，俄联邦侦查委员会25日发布消息说，乌克兰军队无人机当天袭击了位于俄西部斯摩棱斯克州的“多罗戈布日”化工厂，造成7人死亡、至少10人受伤。据该委员会官网消息，至少30架乌军无人机袭击了这家氮肥生产企业，伤亡者均为平民。袭击还造成工厂部分设施被毁。俄联邦侦查委员会调查总局已对此次袭击事件进行立案调查。斯摩棱斯克州州长瓦西里·阿诺欣当天表示，特勤和医务人员正在事发现场救援，袭击引发的火情已被控制，所有伤员已入院治疗。 (新华社)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>财联社2月25日电，稳定币USDC发行商Circle美股盘前涨幅扩大至21%，公司第四季度业绩超市场预期。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>OpenClaw之父给开发者的建议：保持玩乐心 去构建梦寐以求的东西</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>【OpenClaw之父给开发者的建议：保持玩乐心 去构建梦寐以求的东西】财联社2月25日电，当地时间2月24日，OpenClaw之父彼得·斯坦伯格在OpenAI的节目中表示，建议开发者保持玩乐心，去构建梦寐以求的东西，“如果你具备高行动力且够聪明，市场对你的需求将比任何时候都大”。 (澎湃新闻)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>以军称在黎南部发现真主党武装设施 指其违反黎以停火协议</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>【以军称在黎南部发现真主党武装设施 指其违反黎以停火协议】财联社2月25日电，以色列国防军表示，过去数月来，以军在黎巴嫩南部开展行动，发现并拆除了多处武装设施，包括观察哨、射击阵地及反坦克武器。以军称，这些设施属于黎巴嫩真主党，其存在违反了以色列与黎巴嫩之间的停火协议。以军表示，实施多次针对性行动，旨在阻止真主党重新武装，并拆除其在当地的基础设施。以军强调，将继续采取行动，防止真主党恢复并增强其武装能力。黎巴嫩真主党方面暂无回应。 (央视新闻)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>美股加密货币概念股盘前普涨</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>【美股加密货币概念股盘前普涨】财联社2月25日电，比特币小幅上扬，加密货币概念股盘前普涨，Circle合作伙伴Coinbase涨超4.5%，Strategy涨超4%，Robinhood涨超3%。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>【风口研报·洞察】商业航天的新一代“核心基建”，SpaceX引领星间激光通信产业链迎来从0到1突破，规模化部署与成本突破有望驱动千亿市场机遇；两会前后A股的风格</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>①两会前后A股的风格；②商业航天的新一代“核心基建”，SpaceX引领星间激光通信产业链迎来从0到1突破，规模化部署与成本突破有望驱动千亿市场机遇；③今日全市场机构研报共发布82篇，恩捷股份、华绿生物评级得到上调，7家公司获得首度覆盖，其中东方电气等4股获新财富分析师深度覆盖；④在个股机构关注度排行中，中际旭创首次上榜，前五名依次为万辰集团&gt;比亚迪&gt;长城汽车&gt;青岛银行&gt;中际旭创。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>《中华人民共和国和德意志联邦共和国联合新闻声明》发布</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>【《中华人民共和国和德意志联邦共和国联合新闻声明》发布】财联社2月25日电，《中华人民共和国和德意志联邦共和国联合新闻声明》发布。《声明》提出，双方强调经贸合作是双边关系的重要组成部分，愿深化互利共赢合作。双方强调开放对话、公平竞争和相互开放市场至关重要。中方注意到德方重视“降依赖”、贸易不平衡、出口管理等问题，德方注意到中方对经贸问题泛安全化、高技术产品出口管理等关切。双方愿通过坦诚开放对话妥善解决彼此关切，以确保长期、平衡、可信赖、可持续的经贸关系。两国总理共同出席了中德经济顾问委员会座谈会，同两国企业家代表互动交流。双方同意继续开展中德气候变化与绿色转型对话。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>稳定币发行商Circle美股盘前涨超20%</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>【稳定币发行商Circle美股盘前涨超20%】财联社2月25日电，稳定币发行商Circle美股盘前涨超20%，公司2025年第四季度调整后EBITDA为1.67亿美元，同比增长412%。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>财联社2月25日晚间新闻精选</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>【财联社2月25日晚间新闻精选】
@@ -4871,81 +4974,53 @@
 3、在岸人民币兑美元收盘报6.8672，较上一交易日上涨177点，创2023年4月14日以来新高。
 4、存储芯片巨头SK海力士表示，拟在韩国投资150亿美元扩建芯片产能，以满足日益增长的半导体需求。
 5、①格力电器：第一大股东珠海明骏拟减持不超2%公司股份。②顺灏股份：参股公司轨道辰光计划2031年至2035年卫星大规模批量生产并组网发射且在轨对接建成大规模太空数据中心。③ST新华锦：公司及实际控制人因涉嫌信息披露违法违规被中国证监会立案。④海光信息：预计一季度净利同比增长23%到42%。⑤4连板汉缆股份：2025年净利润5.92亿元 同比下降9.59%。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>格力电器回应大股东珠海明骏减持：系正常财务优化</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>【格力电器回应大股东珠海明骏减持：系正常财务优化】财联社2月25日电，格力电器今日公告称，公司第一大股东珠海明骏投资合伙企业(有限合伙)计划通过大宗交易方式减持不超过总股本2%的股份，减持资金用于偿还银行贷款。财联社记者从格力电器方面获悉，本次减持系珠海明骏履行完毕股份锁定承诺后的正常财务安排。本次权益变动后，珠海明骏仍保持格力电器单一第一大股东地位。格力电器表示，此次减持不会导致公司控制权变更，也不会影响公司治理结构和生产经营。(财联社记者 陆婷婷)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>美国抵押贷款利率降至2022年以来最低 刺激再融资活动增加</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>【美国抵押贷款利率降至2022年以来最低 刺激再融资活动增加】财联社2月25日电，美国抵押贷款利率上周小幅下滑至自2022年以来的最低水平，带动再融资活动增加。根据美国抵押贷款银行家协会(MBA)周三公布的数据，截至2月20日当周，30年期抵押贷款的合同利率下降8个基点至6.09%。锁定前5年利率的可调利率抵押贷款的利率降至5.23%，是2022年9月份以来的最低水平。衡量再融资活动的一项指数上涨逾4%，达到5个月来的第二高水平。根据MBA的数据，除两周外，今年其他时间再融资活动均有所增长。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>美股无人机概念股盘前多数上涨</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>【美股无人机概念股盘前多数上涨】财联社2月25日电，美股无人机概念股盘前多数上涨，Joby Aviation涨超6%，与Uber推出应用程序Uber Air，计划今年在迪拜亮相；SES Al Corp、Unusual Machines涨超2%，Ondas、Archer Aviation涨超1%。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>【财联社早知道】151亿美元！SK海力士宣布追加投资扩建HBM工厂，机构预计2026年全球HBM出货量有望达5.7BGB，这家公司的产品已达国际先进水平，且全面覆盖国内主要HBM客户</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>①151亿美元！SK海力士宣布追加投资扩建HBM工厂，机构预计2026年全球HBM出货量有望达5.7BGB，这家公司的产品已达到国际先进水平，目前已全面覆盖国内主要2.5D及HBM客户；
 ②三星即将举办Galaxy全球新品发布会，分析师称消费电子硬件仍然是AI应用落地最为确定的受益方向，这家公司已为国内多家知名手机终端提供多款非晶合金铰链结构件；
 ③这家公司表示DRAM涨价幅度相对较大，Nor Flash也有不同程度的价格调整。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>财联社2月25日电，花旗集团任命哈夫克为全球市场欧洲公司首席执行官。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>用友网络回应Claude系列AI影响：公司BIP具备五大护城河 AI浪潮下将借行业知识实现赶超</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>【用友网络回应Claude系列AI影响：公司BIP具备五大护城河 AI浪潮下将借行业知识实现赶超】财联社2月25日电，有投资者问用友网络(600588)，Anthropic旗下Claude系列AI及智能体技术，已对传统企业服务软件形成颠覆性冲击，甚至可能直接替代传统ERP、财务、人力等管理软件。请问公司是否评估过该类技术对用友现有BIP、YonGPT及核心业务的实质性替代风险？用友网络在互动平台表示，从昨晚发布会来看，Cowork及插件系统不是要把现有软件的功能做完整的替代，而是从底层智能OS和任务编排层的维度，来打造面向知识工作者的企业Agent平台。产品形态保留现有软件作为system of record/专业执行界面，强调与合作企业（如Salesforce）之间的数据和信任关系，因此，美股软件与SaaS板块整体反弹。由此产生的行业冲击更聚焦于简单重复性的执行类工具，对客户核心复杂业务场景的系统介入较低。 用友BIP系列产品具备强大的护城河能力：1.企业管理需要有复杂严谨的逻辑计算，比如排产、成本卷积等，大模型难以实现，还要依赖工程化方式（就是ERP）；2.我们认为随着AI的发展，未来会进入自主决策阶段，AI不仅仅是决策，还可以自主执行，自主执行要调用技能（比如新增单据、自动审核等），这就要求ERP每一个功能都是独立的微服务，BIP基于原生微服务架构，这就是BIP的优势。传统的ERP系统就会被替换为BIP；3.随着AI的发展，数据价值越来越高，多数企业（特别是大客户）内部信息化厂商众多，形成各种历史数据孤岛，BIP统一底座，10大领域，如果统一更换为BIP，数据治理工作量大幅减少；4.AI功能越强，流程×数据×AI优势越明显，AI会更多的融入到流程中，而不是简单的外挂插件，这也是BIP的优势；5.未来的趋势是行业垂类模型，比如医药行业垂类模型（大模型+行业知识+行业管理经验+技能），这里面最难的是行业知识与行业管理经验，用友积累了大量的客户经验数据与行业知识（非外部模型厂商可公开获取），从这些数据知识里面可以推理出行业规则，也代表了用友未来最有可能成为行业垂类模型厂商。 综上，用友不仅不会在AI浪潮下被大模型厂商颠覆，更会借助深耕行业所产生的数据积累、业务理解叠加AI能力形成全面赶超。</t>
-  </si>
-  <si>
-    <t>美驻以使馆扩大领事服务范围遭指责：违反国际法原则</t>
-  </si>
-  <si>
-    <t>【美驻以使馆扩大领事服务范围遭指责：违反国际法原则】财联社2月25日电，巴勒斯坦官方机构“反对隔离墙和定居点委员会”发表声明表示，美国驻以色列大使馆决定将领事服务扩大至位于约旦河西岸南部的犹太人定居点埃夫拉特，此举违反国际法原则，并被视为对以色列定居点政策的“事实性支持”。 (央视新闻)</t>
-  </si>
-  <si>
-    <t>美股盘前要闻一览</t>
-  </si>
-  <si>
-    <t>【美股盘前要闻一览】财联社2月25日电，投资者需重点关注的美股市场财经要闻如下：
-1、美国三大股指期货集体上涨。道琼斯指数期货涨0.34%，标普500指数期货涨0.35%，纳斯达克100指数期货涨0.45%。
-2、欧洲主要股指集体走高。英国富时100指数涨0.97%，法国CAC40指数涨0.42%，德国DAX30指数涨0.28%。
-3、国际原油日内上涨。WTI原油涨0.90%，报66.218美元/桶；布伦特原油涨0.97%，报71.262美元/桶。
-4、交易员削减对美联储的降息押注，认为6月降息25个基点的概率为50%。
-5、英伟达即将于北京时间周四早间公布2025财年第四财季财报。市场预期其收入将增长至636亿美元，同比增长68.3%。
-6、美股锂矿板块盘前走强。消息面上，津巴布韦矿业部宣布立即暂停所有原矿及锂精矿出口。
-7、由于缺乏实质证据，美国法院暂时驳回xAI针对OpenAI的商业机密侵权指控。
-8、美国房利美、房地美据悉"非常有可能"今年上市，估值达5000亿至7000亿美元。
-9、稳定币USDC发行商Circle美股盘前涨超15%，公司第四季度业绩超市场预期。
-10、美股光通信龙头Lumentum盘前涨幅扩大至2%，此前花旗维持其“买入”评级，目标价上调至800美元。</t>
-  </si>
-  <si>
-    <t>*ST宇顺：公司间接持有盛合晶微约0.2058%股份</t>
-  </si>
-  <si>
-    <t>【*ST宇顺：公司间接持有盛合晶微约0.2058%股份】财联社2月25日电，*ST宇顺(002289.SZ)公告称，公司参股的长芯贰号基金投资的盛合晶微首次公开发行股票并在科创板上市申请获上市委审议通过。公司间接持有盛合晶微约330.72万股，持股比例约0.2058%。盛合晶微本次公开发行股票并上市尚需取得中国证监会同意注册的决定，存在不确定性。</t>
-  </si>
-  <si>
-    <t>财联社2月25日电，现货钯金日内涨超4%，现报1852.19美元/盎司。</t>
-  </si>
-  <si>
-    <t>财联社2月25日电，城堡证券反驳Citrini报告，认为人工智能不太可能引发大规模失业。</t>
-  </si>
-  <si>
-    <t>财联社2月25日电，纳斯达克中国金龙指数跌幅扩大，现跌1.0%，最新报7504.6点。</t>
-  </si>
-  <si>
-    <t>中国石油</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -5819,7 +5894,7 @@
         <v>601857</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>1318</v>
+        <v>1229</v>
       </c>
       <c r="C9" s="7">
         <v>-0.9</v>
@@ -35434,48 +35509,42 @@
       </c>
     </row>
     <row r="2" spans="1:4" ht="94" customHeight="1">
+      <c r="A2" s="3" t="s">
+        <v>1230</v>
+      </c>
       <c r="B2" s="5" t="s">
-        <v>1317</v>
+        <v>1231</v>
       </c>
       <c r="C2" s="6">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="D2" s="17">
-        <v>0.98585648148148153</v>
+        <v>1.1898148148148149E-2</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="94" customHeight="1">
-      <c r="A3" s="3" t="s">
-        <v>1229</v>
-      </c>
       <c r="B3" s="5" t="s">
-        <v>1230</v>
+        <v>1232</v>
       </c>
       <c r="C3" s="6">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="D3" s="17">
-        <v>0.98428240740740736</v>
+        <v>4.2245370370370371E-3</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="94" customHeight="1">
-      <c r="A4" s="3" t="s">
-        <v>1231</v>
-      </c>
       <c r="B4" s="5" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="C4" s="6">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="D4" s="17">
-        <v>0.97952546296296295</v>
+        <v>1.9675925925925924E-3</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="94" customHeight="1">
-      <c r="A5" s="3" t="s">
-        <v>1233</v>
-      </c>
       <c r="B5" s="5" t="s">
         <v>1234</v>
       </c>
@@ -35483,7 +35552,7 @@
         <v>46078</v>
       </c>
       <c r="D5" s="17">
-        <v>0.97908564814814814</v>
+        <v>0.99828703703703703</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="94" customHeight="1">
@@ -35497,94 +35566,94 @@
         <v>46078</v>
       </c>
       <c r="D6" s="17">
-        <v>0.97253472222222226</v>
+        <v>0.99211805555555554</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="94" customHeight="1">
-      <c r="A7" s="3" t="s">
+      <c r="B7" s="5" t="s">
         <v>1237</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>1238</v>
       </c>
       <c r="C7" s="6">
         <v>46078</v>
       </c>
       <c r="D7" s="17">
-        <v>0.96829861111111115</v>
+        <v>0.98585648148148153</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="94" customHeight="1">
       <c r="A8" s="3" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>1239</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>1240</v>
       </c>
       <c r="C8" s="6">
         <v>46078</v>
       </c>
       <c r="D8" s="17">
-        <v>0.9655555555555555</v>
+        <v>0.98428240740740736</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="94" customHeight="1">
       <c r="A9" s="3" t="s">
+        <v>1240</v>
+      </c>
+      <c r="B9" s="5" t="s">
         <v>1241</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>1242</v>
       </c>
       <c r="C9" s="6">
         <v>46078</v>
       </c>
       <c r="D9" s="17">
-        <v>0.96125000000000005</v>
+        <v>0.97952546296296295</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="94" customHeight="1">
       <c r="A10" s="3" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B10" s="5" t="s">
         <v>1243</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>1244</v>
       </c>
       <c r="C10" s="6">
         <v>46078</v>
       </c>
       <c r="D10" s="17">
-        <v>0.95983796296296298</v>
+        <v>0.97908564814814814</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="94" customHeight="1">
       <c r="A11" s="3" t="s">
+        <v>1244</v>
+      </c>
+      <c r="B11" s="5" t="s">
         <v>1245</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>1246</v>
       </c>
       <c r="C11" s="6">
         <v>46078</v>
       </c>
       <c r="D11" s="17">
-        <v>0.9561574074074074</v>
+        <v>0.97253472222222226</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="94" customHeight="1">
       <c r="A12" s="3" t="s">
+        <v>1246</v>
+      </c>
+      <c r="B12" s="5" t="s">
         <v>1247</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>1248</v>
       </c>
       <c r="C12" s="6">
         <v>46078</v>
       </c>
       <c r="D12" s="17">
-        <v>0.95402777777777781</v>
+        <v>0.96829861111111115</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="94" customHeight="1">
+      <c r="A13" s="3" t="s">
+        <v>1248</v>
+      </c>
       <c r="B13" s="5" t="s">
         <v>1249</v>
       </c>
@@ -35592,7 +35661,7 @@
         <v>46078</v>
       </c>
       <c r="D13" s="17">
-        <v>0.9493287037037037</v>
+        <v>0.9655555555555555</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="94" customHeight="1">
@@ -35606,52 +35675,52 @@
         <v>46078</v>
       </c>
       <c r="D14" s="17">
-        <v>0.945775462962963</v>
+        <v>0.96125000000000005</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="94" customHeight="1">
+      <c r="A15" s="3" t="s">
+        <v>1252</v>
+      </c>
       <c r="B15" s="5" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="C15" s="6">
         <v>46078</v>
       </c>
       <c r="D15" s="17">
-        <v>0.94291666666666663</v>
+        <v>0.95983796296296298</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="94" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="C16" s="6">
         <v>46078</v>
       </c>
       <c r="D16" s="17">
-        <v>0.94108796296296293</v>
+        <v>0.9561574074074074</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="94" customHeight="1">
       <c r="A17" s="3" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="C17" s="6">
         <v>46078</v>
       </c>
       <c r="D17" s="17">
-        <v>0.93956018518518514</v>
+        <v>0.95402777777777781</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="94" customHeight="1">
-      <c r="A18" s="3" t="s">
-        <v>1257</v>
-      </c>
       <c r="B18" s="5" t="s">
         <v>1258</v>
       </c>
@@ -35659,24 +35728,24 @@
         <v>46078</v>
       </c>
       <c r="D18" s="17">
-        <v>0.93952546296296291</v>
+        <v>0.9493287037037037</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="94" customHeight="1">
+      <c r="A19" s="3" t="s">
+        <v>1259</v>
+      </c>
       <c r="B19" s="5" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="C19" s="6">
         <v>46078</v>
       </c>
       <c r="D19" s="17">
-        <v>0.93883101851851847</v>
+        <v>0.945775462962963</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="94" customHeight="1">
-      <c r="A20" s="3" t="s">
-        <v>1260</v>
-      </c>
       <c r="B20" s="5" t="s">
         <v>1261</v>
       </c>
@@ -35684,7 +35753,7 @@
         <v>46078</v>
       </c>
       <c r="D20" s="17">
-        <v>0.93790509259259258</v>
+        <v>0.94291666666666663</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="94" customHeight="1">
@@ -35698,7 +35767,7 @@
         <v>46078</v>
       </c>
       <c r="D21" s="17">
-        <v>0.93487268518518518</v>
+        <v>0.94108796296296293</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="94" customHeight="1">
@@ -35712,7 +35781,7 @@
         <v>46078</v>
       </c>
       <c r="D22" s="17">
-        <v>0.92706018518518518</v>
+        <v>0.93956018518518514</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="94" customHeight="1">
@@ -35726,38 +35795,38 @@
         <v>46078</v>
       </c>
       <c r="D23" s="17">
-        <v>0.92412037037037043</v>
+        <v>0.93952546296296291</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="94" customHeight="1">
-      <c r="A24" s="3" t="s">
+      <c r="B24" s="5" t="s">
         <v>1268</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>1269</v>
       </c>
       <c r="C24" s="6">
         <v>46078</v>
       </c>
       <c r="D24" s="17">
-        <v>0.92305555555555552</v>
+        <v>0.93883101851851847</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="94" customHeight="1">
       <c r="A25" s="3" t="s">
+        <v>1269</v>
+      </c>
+      <c r="B25" s="5" t="s">
         <v>1270</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>1271</v>
       </c>
       <c r="C25" s="6">
         <v>46078</v>
       </c>
       <c r="D25" s="17">
-        <v>0.92254629629629625</v>
+        <v>0.93790509259259258</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="94" customHeight="1">
+      <c r="A26" s="3" t="s">
+        <v>1271</v>
+      </c>
       <c r="B26" s="5" t="s">
         <v>1272</v>
       </c>
@@ -35765,77 +35834,77 @@
         <v>46078</v>
       </c>
       <c r="D26" s="17">
-        <v>0.92138888888888892</v>
+        <v>0.93487268518518518</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="94" customHeight="1">
+      <c r="A27" s="3" t="s">
+        <v>1273</v>
+      </c>
       <c r="B27" s="5" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="C27" s="6">
         <v>46078</v>
       </c>
       <c r="D27" s="17">
-        <v>0.91783564814814811</v>
+        <v>0.92706018518518518</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="94" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="C28" s="6">
         <v>46078</v>
       </c>
       <c r="D28" s="17">
-        <v>0.91704861111111113</v>
+        <v>0.92412037037037043</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="94" customHeight="1">
+      <c r="A29" s="3" t="s">
+        <v>1277</v>
+      </c>
       <c r="B29" s="5" t="s">
-        <v>1276</v>
+        <v>1278</v>
       </c>
       <c r="C29" s="6">
         <v>46078</v>
       </c>
       <c r="D29" s="17">
-        <v>0.91689814814814818</v>
+        <v>0.92305555555555552</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="94" customHeight="1">
       <c r="A30" s="3" t="s">
-        <v>1277</v>
+        <v>1279</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>1278</v>
+        <v>1280</v>
       </c>
       <c r="C30" s="6">
         <v>46078</v>
       </c>
       <c r="D30" s="17">
-        <v>0.91644675925925922</v>
+        <v>0.92254629629629625</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="94" customHeight="1">
-      <c r="A31" s="3" t="s">
-        <v>1279</v>
-      </c>
       <c r="B31" s="5" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="C31" s="6">
         <v>46078</v>
       </c>
       <c r="D31" s="17">
-        <v>0.9133796296296296</v>
+        <v>0.92138888888888892</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="94" customHeight="1">
-      <c r="A32" s="3" t="s">
-        <v>1281</v>
-      </c>
       <c r="B32" s="5" t="s">
         <v>1282</v>
       </c>
@@ -35843,24 +35912,24 @@
         <v>46078</v>
       </c>
       <c r="D32" s="17">
-        <v>0.91273148148148153</v>
+        <v>0.91783564814814811</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="94" customHeight="1">
+      <c r="A33" s="3" t="s">
+        <v>1283</v>
+      </c>
       <c r="B33" s="5" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="C33" s="6">
         <v>46078</v>
       </c>
       <c r="D33" s="17">
-        <v>0.91249999999999998</v>
+        <v>0.91704861111111113</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="94" customHeight="1">
-      <c r="A34" s="3" t="s">
-        <v>1284</v>
-      </c>
       <c r="B34" s="5" t="s">
         <v>1285</v>
       </c>
@@ -35868,7 +35937,7 @@
         <v>46078</v>
       </c>
       <c r="D34" s="17">
-        <v>0.91063657407407406</v>
+        <v>0.91689814814814818</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="94" customHeight="1">
@@ -35882,7 +35951,7 @@
         <v>46078</v>
       </c>
       <c r="D35" s="17">
-        <v>0.90815972222222219</v>
+        <v>0.91644675925925922</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="94" customHeight="1">
@@ -35896,7 +35965,7 @@
         <v>46078</v>
       </c>
       <c r="D36" s="17">
-        <v>0.90748842592592593</v>
+        <v>0.9133796296296296</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="94" customHeight="1">
@@ -35910,108 +35979,108 @@
         <v>46078</v>
       </c>
       <c r="D37" s="17">
-        <v>0.90703703703703709</v>
+        <v>0.91273148148148153</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="94" customHeight="1">
-      <c r="A38" s="3" t="s">
+      <c r="B38" s="5" t="s">
         <v>1292</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>1293</v>
       </c>
       <c r="C38" s="6">
         <v>46078</v>
       </c>
       <c r="D38" s="17">
-        <v>0.90642361111111114</v>
+        <v>0.91249999999999998</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="94" customHeight="1">
       <c r="A39" s="3" t="s">
+        <v>1293</v>
+      </c>
+      <c r="B39" s="5" t="s">
         <v>1294</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>1295</v>
       </c>
       <c r="C39" s="6">
         <v>46078</v>
       </c>
       <c r="D39" s="17">
-        <v>0.90607638888888886</v>
+        <v>0.91063657407407406</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="94" customHeight="1">
       <c r="A40" s="3" t="s">
+        <v>1295</v>
+      </c>
+      <c r="B40" s="5" t="s">
         <v>1296</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>1297</v>
       </c>
       <c r="C40" s="6">
         <v>46078</v>
       </c>
       <c r="D40" s="17">
-        <v>0.90349537037037042</v>
+        <v>0.90815972222222219</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="94" customHeight="1">
       <c r="A41" s="3" t="s">
+        <v>1297</v>
+      </c>
+      <c r="B41" s="5" t="s">
         <v>1298</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>1299</v>
       </c>
       <c r="C41" s="6">
         <v>46078</v>
       </c>
       <c r="D41" s="17">
-        <v>0.89656250000000004</v>
+        <v>0.90748842592592593</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="94" customHeight="1">
       <c r="A42" s="3" t="s">
+        <v>1299</v>
+      </c>
+      <c r="B42" s="5" t="s">
         <v>1300</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>1301</v>
       </c>
       <c r="C42" s="6">
         <v>46078</v>
       </c>
       <c r="D42" s="17">
-        <v>0.89629629629629626</v>
+        <v>0.90703703703703709</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="94" customHeight="1">
       <c r="A43" s="3" t="s">
+        <v>1301</v>
+      </c>
+      <c r="B43" s="5" t="s">
         <v>1302</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>1303</v>
       </c>
       <c r="C43" s="6">
         <v>46078</v>
       </c>
       <c r="D43" s="17">
-        <v>0.89497685185185183</v>
+        <v>0.90642361111111114</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="94" customHeight="1">
       <c r="A44" s="3" t="s">
+        <v>1303</v>
+      </c>
+      <c r="B44" s="5" t="s">
         <v>1304</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>1305</v>
       </c>
       <c r="C44" s="6">
         <v>46078</v>
       </c>
       <c r="D44" s="17">
-        <v>0.8934375</v>
+        <v>0.90607638888888886</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="94" customHeight="1">
+      <c r="A45" s="3" t="s">
+        <v>1305</v>
+      </c>
       <c r="B45" s="5" t="s">
         <v>1306</v>
       </c>
@@ -36019,7 +36088,7 @@
         <v>46078</v>
       </c>
       <c r="D45" s="17">
-        <v>0.89336805555555554</v>
+        <v>0.90349537037037042</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="94" customHeight="1">
@@ -36033,7 +36102,7 @@
         <v>46078</v>
       </c>
       <c r="D46" s="17">
-        <v>0.88909722222222221</v>
+        <v>0.89656250000000004</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="94" customHeight="1">
@@ -36047,7 +36116,7 @@
         <v>46078</v>
       </c>
       <c r="D47" s="17">
-        <v>0.88525462962962964</v>
+        <v>0.89629629629629626</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="94" customHeight="1">
@@ -36061,7 +36130,7 @@
         <v>46078</v>
       </c>
       <c r="D48" s="17">
-        <v>0.88344907407407403</v>
+        <v>0.89497685185185183</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="94" customHeight="1">
@@ -36075,7 +36144,7 @@
         <v>46078</v>
       </c>
       <c r="D49" s="17">
-        <v>0.88233796296296296</v>
+        <v>0.8934375</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="94" customHeight="1">
@@ -36086,18 +36155,21 @@
         <v>46078</v>
       </c>
       <c r="D50" s="17">
-        <v>0.88059027777777776</v>
+        <v>0.89336805555555554</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="94" customHeight="1">
+      <c r="A51" s="3" t="s">
+        <v>1316</v>
+      </c>
       <c r="B51" s="5" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="C51" s="6">
         <v>46078</v>
       </c>
       <c r="D51" s="17">
-        <v>0.87962962962962965</v>
+        <v>0.88909722222222221</v>
       </c>
     </row>
   </sheetData>
